--- a/05_Figures/F06_prediction/proteins/total/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/d_mcsa/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -128,469 +128,502 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">HNRNPH1</t>
+  </si>
+  <si>
     <t xml:space="preserve">NTPCR</t>
   </si>
   <si>
-    <t xml:space="preserve">HNRNPH1</t>
+    <t xml:space="preserve">UBAC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHD2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLCL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDE</t>
   </si>
   <si>
     <t xml:space="preserve">MRPS27</t>
   </si>
   <si>
-    <t xml:space="preserve">UBAC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAHD2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDE</t>
-  </si>
-  <si>
     <t xml:space="preserve">PGAM2</t>
   </si>
   <si>
+    <t xml:space="preserve">ATP5ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EML1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERO1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIST2H2BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSDL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBPL1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPA2</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAB2B</t>
   </si>
   <si>
-    <t xml:space="preserve">TIMM10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERO1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIST2H2BE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSDL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSBPL1A</t>
+    <t xml:space="preserve">RPL14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS6KA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAP1L1</t>
   </si>
   <si>
     <t xml:space="preserve">PHKA1</t>
   </si>
   <si>
-    <t xml:space="preserve">PPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS6KA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EML1</t>
+    <t xml:space="preserve">PHKB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPCS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMC1</t>
   </si>
   <si>
     <t xml:space="preserve">FITM1</t>
   </si>
   <si>
-    <t xml:space="preserve">NAP1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPCS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THOP1</t>
+    <t xml:space="preserve">GPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRRC20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN2</t>
   </si>
   <si>
     <t xml:space="preserve">TRMT10C</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRSF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYPL1</t>
+    <t xml:space="preserve">BZW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD63</t>
   </si>
   <si>
     <t xml:space="preserve">GAPDH</t>
   </si>
   <si>
-    <t xml:space="preserve">LRRC20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGP</t>
+    <t xml:space="preserve">GPAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACROD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS4X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMYD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKBP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFAP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACOT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATPAF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPNT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLCC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJB4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJC19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDXR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFITM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISOC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYL6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIPSNAP3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NNMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCYT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGPEP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTGR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RASA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDH11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMIM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPPL2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTBN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRSF3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMED9</t>
   </si>
   <si>
     <t xml:space="preserve">TMLHE</t>
   </si>
   <si>
-    <t xml:space="preserve">AAMDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BZW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLCL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS4X</t>
-  </si>
-  <si>
     <t xml:space="preserve">TPI1</t>
   </si>
   <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDXR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACROD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFAP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMYD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACOT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATPAF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLCC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DECR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJC19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERMT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFITM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISOC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPDU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYL6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIPSNAP3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NNMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFDN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKFB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGPEP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM20D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTGR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RASA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDH11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHOC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMIM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTBN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRSF3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TACO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAP4</t>
+    <t xml:space="preserve">TYMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAMP2</t>
   </si>
 </sst>
 </file>
@@ -977,16 +1010,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.411542597430573</v>
+        <v>-0.364538777407582</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0153846153846154</v>
+        <v>-0.0857142857142857</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1010,29 +1043,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.411542597430573</v>
+        <v>-0.364538777407582</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0153846153846154</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.388059701492537</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.402985074626866</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.689640192990216</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.677034040376926</v>
-      </c>
+        <v>-0.0857142857142857</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1056,2206 +1081,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.86075144872368</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.520259523849437</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.166905381172802</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.308667364449831</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.0257518514743114</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.538651246515712</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.12660874414488</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.0896390790014314</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.559336609886812</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.456589947832457</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0781355153290101</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.189311845557727</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.297782303081048</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.280315259041463</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.32085363681084</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.548001695308545</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.463716611294454</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.987644193896718</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.120779743128806</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.837733258344963</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.349619764264675</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.372059860548061</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.29729197031108</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.174163432010258</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-1.73375091502235</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.103327551031141</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-3.23502693080249</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.221991260942619</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.661801726495404</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-2.03477992654029</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.823157614695423</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.357234525229899</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.54554625489402</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.282649486037825</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.380873588123485</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.544133029568901</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-1.07314897549101</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.25991073807159</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.685550993955256</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.419293764153803</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.52236099080488</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.242953071681237</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.692102944696372</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.600433504089216</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.07349486104606</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.488616493723043</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.608809605946661</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.0447846506943796</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.1475404608492</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.072655101232505</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.11312199829268</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.512357595552649</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.434345456611307</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.12938149775868</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.111263297361197</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.387522966626888</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.475491892166041</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.83526849625231</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.0155208250793382</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.422137331949153</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.284893979782259</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-2.40563149673671</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.538863394805925</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.00047032659563</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.0698855232954263</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-1.10634926530096</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-1.21131671863047</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.34447073160445</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.817385382712683</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.17100078248811</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.252547123755812</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.4182161975939</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.97837840305811</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.021979910055685</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.37236050585918</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.389470065278325</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.14791713467381</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.435480045208055</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.283892841375098</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.0812592941786503</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.640511702939818</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.742287032879515</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.66237357408024</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.09574695376469</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.00152970629745985</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.654729701565387</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.256009380738494</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.574462821782039</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.103505264567865</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.0130062224963454</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.40708037554898</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.359479169709955</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.172352328338911</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.52505880464372</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.267554877501343</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.0130206744953183</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.853433749684448</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.00701455605994794</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-2.35816719699556</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.217539525305515</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.564220085610233</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-1.11514614443055</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.83617104774501</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.455275593832286</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.663347694209835</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.546233176655803</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-1.96352614134329</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.843603341794728</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.189431142481656</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.94968996401797</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.28512773900681</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.888522893608629</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.201897884844193</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.625273322396372</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.45011446984493</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.318918722754043</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.216134182842346</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0.0572163868365001</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0.0394311256203294</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.00792625557799376</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.351999123023908</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.00371533664582924</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.79274440430173</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.22059486399895</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.449554100534626</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.766387496317842</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.488323057943084</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.763258105023372</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.542428901280895</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.81082200227044</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.261908744502038</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.73319047078154</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.21065159212329</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.96631018907575</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-2.24896564568358</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.67014523393034</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.959956841795708</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.64181836816116</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.407381073932087</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.0911173624359216</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.965275019085151</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.767417649561652</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.83646219645471</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.0594982054780662</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.33398237476013</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.271560552701269</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.71799829152887</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.5041187300566</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.563686799338318</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-1.11595509867632</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.518617549659358</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.016801937454463</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.52133913184413</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.46170753617143</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-2.2360715580085</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.76509406877797</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.284779710221065</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.5011867051394</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-1.04481390979063</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.849525537567167</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-1.30560003991096</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-1.38013453490418</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.00549113783655142</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-2.26815106837449</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.751903479495731</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>0.0976634250775442</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.482247264195759</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.988213363360128</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.930222942845945</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>0.503251005322108</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.71974959790943</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.195663734388754</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.466201815469919</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.618896657257845</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.849983371234393</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-1.28121637489939</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.903885038811067</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.943986302507968</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.39372562506911</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.374501121247773</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.801384215882244</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.242228505567157</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0.0670935644838444</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-2.08097842107543</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.16200760468375</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.763293730439764</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.12877805225982</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-2.17327477847599</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.479630948334346</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.56762997523155</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.0834038629907139</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.937799493617893</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.693408230034789</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.0584832720609052</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>0.179442226226163</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.611840013649698</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.245744075330988</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.59838646119287</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.047731208352146</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>0.365773761122442</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3298,7 +1123,7 @@
         <v>1.706</v>
       </c>
       <c r="E2" t="n">
-        <v>1.99360144703202</v>
+        <v>1.98693722134188</v>
       </c>
     </row>
     <row r="3">
@@ -3315,7 +1140,7 @@
         <v>4.218</v>
       </c>
       <c r="E3" t="n">
-        <v>1.85458566642778</v>
+        <v>1.51864193138696</v>
       </c>
     </row>
     <row r="4">
@@ -3332,7 +1157,7 @@
         <v>1.578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.687662727755726</v>
+        <v>0.531860758634678</v>
       </c>
     </row>
     <row r="5">
@@ -3349,7 +1174,7 @@
         <v>3.683</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.415428722461504</v>
+        <v>-0.107921030711014</v>
       </c>
     </row>
     <row r="6">
@@ -3366,7 +1191,7 @@
         <v>2.983</v>
       </c>
       <c r="E6" t="n">
-        <v>3.02840623542895</v>
+        <v>2.84226519479732</v>
       </c>
     </row>
     <row r="7">
@@ -3383,7 +1208,7 @@
         <v>2.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.745618415657705</v>
+        <v>1.07097218539273</v>
       </c>
     </row>
     <row r="8">
@@ -3400,7 +1225,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>1.09008150016455</v>
+        <v>1.13988828588456</v>
       </c>
     </row>
     <row r="9">
@@ -3417,7 +1242,7 @@
         <v>-1.918</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8350358898379</v>
+        <v>1.85382428864545</v>
       </c>
     </row>
     <row r="10">
@@ -3434,7 +1259,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.854057696517967</v>
+        <v>0.801757520308933</v>
       </c>
     </row>
     <row r="11">
@@ -3451,7 +1276,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>1.58537992796307</v>
+        <v>1.63913363572884</v>
       </c>
     </row>
     <row r="12">
@@ -3468,7 +1293,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.17976858162378</v>
+        <v>2.18085033467197</v>
       </c>
     </row>
     <row r="13">
@@ -3485,7 +1310,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8171012606019</v>
+        <v>2.80514266861509</v>
       </c>
     </row>
     <row r="14">
@@ -3502,7 +1327,7 @@
         <v>1.311</v>
       </c>
       <c r="E14" t="n">
-        <v>0.588954717588659</v>
+        <v>0.637405561008868</v>
       </c>
     </row>
     <row r="15">
@@ -3519,7 +1344,7 @@
         <v>2.862</v>
       </c>
       <c r="E15" t="n">
-        <v>0.589251067992919</v>
+        <v>0.790145163229772</v>
       </c>
     </row>
   </sheetData>
@@ -3578,10 +1403,10 @@
         <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3595,10 +1420,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3612,10 +1437,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="6">
@@ -3629,10 +1454,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.785714285714286</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="7">
@@ -3646,10 +1471,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +1488,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +1505,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="10">
@@ -3697,10 +1522,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.714285714285714</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="11">
@@ -3714,10 +1539,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.714285714285714</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -3731,10 +1556,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.714285714285714</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="13">
@@ -3748,10 +1573,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -3765,10 +1590,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="15">
@@ -3782,10 +1607,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="16">
@@ -3799,10 +1624,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.642857142857143</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="17">
@@ -3816,10 +1641,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="18">
@@ -3833,10 +1658,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -3850,10 +1675,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="20">
@@ -3867,10 +1692,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="21">
@@ -3884,10 +1709,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="22">
@@ -3901,10 +1726,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="23">
@@ -3918,10 +1743,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="24">
@@ -3935,10 +1760,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="25">
@@ -3952,10 +1777,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="26">
@@ -3969,10 +1794,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="27">
@@ -3986,10 +1811,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0.571428571428571</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="28">
@@ -4003,10 +1828,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>0.571428571428571</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="29">
@@ -4020,10 +1845,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="30">
@@ -4037,10 +1862,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="31">
@@ -4054,10 +1879,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="32">
@@ -4071,10 +1896,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="33">
@@ -4088,10 +1913,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="34">
@@ -4105,10 +1930,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="35">
@@ -4122,10 +1947,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="36">
@@ -4241,10 +2066,10 @@
         <v>77</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="43">
@@ -4258,10 +2083,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="44">
@@ -4275,10 +2100,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="45">
@@ -4326,10 +2151,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="48">
@@ -4343,10 +2168,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="49">
@@ -4360,10 +2185,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="50">
@@ -4377,10 +2202,10 @@
         <v>85</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="51">
@@ -4394,10 +2219,10 @@
         <v>86</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="52">
@@ -4496,10 +2321,10 @@
         <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="58">
@@ -4513,10 +2338,10 @@
         <v>93</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="59">
@@ -4530,10 +2355,10 @@
         <v>94</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="60">
@@ -4547,10 +2372,10 @@
         <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="61">
@@ -4564,10 +2389,10 @@
         <v>96</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="62">
@@ -4581,10 +2406,10 @@
         <v>97</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="63">
@@ -4598,10 +2423,10 @@
         <v>98</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="64">
@@ -4615,10 +2440,10 @@
         <v>99</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="65">
@@ -4819,10 +2644,10 @@
         <v>111</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="77">
@@ -6182,6 +4007,193 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="s">
+        <v>192</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>193</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="s">
+        <v>194</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="s">
+        <v>195</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="s">
+        <v>196</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="s">
+        <v>197</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="s">
+        <v>198</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>199</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="s">
+        <v>200</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="s">
+        <v>201</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="s">
+        <v>202</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/total/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/d_mcsa/spls/c_data/results.xlsx
@@ -1046,7 +1046,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.364538777407582</v>
@@ -1054,10 +1054,18 @@
       <c r="I3" t="n">
         <v>-0.0857142857142857</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.343283582089552</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.462686567164179</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.692285382423869</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.675683580588516</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1081,6 +1089,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.54110670638219</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.525757231863192</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.0811979523328725</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.191006684602435</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00850232660404115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.684001597168447</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.26977762058484</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.34784220910721</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.5753574293901</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.567433993966726</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0281592662321372</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.15550836043364</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.385500447937754</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.35547732585566</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.340740621138171</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.672315656687398</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.947553677380788</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.795437324129232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.0968610195719777</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.773398818634781</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.941500501219426</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.235015991985954</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.576536217195279</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.297671076076785</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.71950724241587</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0942898741028078</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-3.25575738007429</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.239220864558612</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.57657456896414</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.87791455816285</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.776149666338588</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.223178798677842</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.41516913717973</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.542434301923385</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.602558665170198</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.691583859152165</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.882810745210493</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.23623546481682</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.814793453746551</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.577459393106416</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.68802272553777</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.261876366871067</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.753074234377324</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.486358590652348</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.892260912050502</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.637762985623415</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.73733764250936</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.0544167881732034</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.22569330842575</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0000286812792799074</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.0555408814989</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.726075937155165</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0982270969989048</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.25774913258707</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.152085065978471</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.477400010633842</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.459172417284266</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.8356707348279</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.471612877518472</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.518841227461411</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.384622025460631</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-2.32575140941495</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.672308782292882</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.2114590355431</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0413031617810444</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-1.14298886705196</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.33648215293946</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.44267477503173</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.795014471048765</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.37252284701888</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.301225296747461</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.53371284473537</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.5811841316351</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.0186547796081186</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.263697087460939</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.426276120338533</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.35761023299958</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.438316857441483</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.336845151401615</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0858756112412622</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.367145769681319</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.727494697575172</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.540715865283381</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.81297548482198</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.0665625086892203</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.552713449639084</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.199153604094883</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.496049968096891</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.1181493886509</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.159061638324356</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.28908987010413</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.165418366219169</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.15584573987324</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.75357279301891</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.252823395088561</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.00542997488522612</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.506901855303191</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.063268561353699</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.60462818587423</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.253192375685953</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.349787445655634</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.709670036100465</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.70423274512802</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.71589578762532</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.840579671426311</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.823239729541721</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.95188522052364</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.652299855239708</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.13043776852755</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.79307671953434</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.04315811937344</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.837105244078847</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.200082840683343</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.616234945280607</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.470973504219204</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.239564217549558</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.311820635006843</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.0732472935942307</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.128678629797683</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.0909618866954521</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.528792227120157</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.0733540579704244</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.72292142856317</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.169211908033815</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.451157474885213</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.36621928389601</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.646871207471995</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.591446483535649</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.686103506423273</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.56653756208758</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.256734199420488</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.23152009513313</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.586433653309928</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.96970244760842</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.98181503116158</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.31906269134706</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.864376851349449</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.60276780637205</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.468378929475152</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.0482897881528905</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.03219100161602</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.758085235937946</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.73635904917801</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.0580925850846017</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.07898644441807</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.314353746447318</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.54947835809754</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.69852833269042</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.655692727971051</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-1.50977761472351</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.59540145175126</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.0838663548149368</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.54381585217183</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.519310282140848</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-2.30259923683871</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.847468531907498</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.274750172844874</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.35606349157086</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.665177972847133</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.12997172044118</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.748506746184731</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-1.34302866139424</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.0272774792710366</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-2.25771626306918</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.823420539143995</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.00399419500157427</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.455251005225334</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.966711925700857</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.793791033581133</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.59129398554053</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-2.04983052430283</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.0786801058995801</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.0115612426633958</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.814138344123805</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.788779005885809</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.29794439025417</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.88503805343923</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.571360326925646</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.0146686707165116</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.403274405643034</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.517932147114063</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.0676744370406218</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.0866459384512994</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.98577837780303</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.26159929596569</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.749474509886849</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.28623806704401</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-2.20375497967169</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.439349980542822</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.586897586752021</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.0949509394469321</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.824560961367821</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.690077810664902</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.257547485086936</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.134910737137241</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.708040602542031</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.229043825087915</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.55681913184716</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.179603140455079</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.362219226555407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
